--- a/DATASOURCE.xlsx
+++ b/DATASOURCE.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30125"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EAE0BDB8-E038-45D2-B8B8-E62FBBC35DBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3B59E5F3-156E-4E00-881B-82CC51C71E19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="5" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SETS" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="53">
   <si>
     <t>PLANTA</t>
   </si>
@@ -146,6 +146,12 @@
   </si>
   <si>
     <t>COSTO_LD_SF</t>
+  </si>
+  <si>
+    <t>38.61</t>
+  </si>
+  <si>
+    <t>34.75</t>
   </si>
   <si>
     <t>COSTO</t>
@@ -523,7 +529,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -577,12 +583,18 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1287,40 +1299,42 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr defaultColWidth="10.5703125" defaultRowHeight="13.9"/>
   <cols>
-    <col min="2" max="2" width="22.7109375" customWidth="1"/>
+    <col min="1" max="1" width="10.5703125" style="44"/>
+    <col min="2" max="2" width="22.7109375" style="44" customWidth="1"/>
     <col min="3" max="3" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="27" t="s">
+      <c r="B1" s="43" t="s">
         <v>29</v>
       </c>
       <c r="K1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="27" t="s">
+    <row r="2" spans="1:11" ht="15">
+      <c r="A2" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="27">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="27" t="s">
+      <c r="B2" s="43" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="15">
+      <c r="A3" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="27">
-        <v>18</v>
-      </c>
-    </row>
+      <c r="B3" s="43" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="15"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -1351,16 +1365,16 @@
         <v>1</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G1" s="27" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H1" s="27" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I1" s="27" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3690,15 +3704,15 @@
         <v>26</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F1" s="39" t="s">
-        <v>36</v>
-      </c>
-      <c r="G1" s="39"/>
+        <v>37</v>
+      </c>
+      <c r="F1" s="42" t="s">
+        <v>38</v>
+      </c>
+      <c r="G1" s="42"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="5" t="s">
@@ -3712,7 +3726,7 @@
         <v>802978.3523250001</v>
       </c>
       <c r="F2" s="18" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G2" s="19">
         <v>0.03</v>
@@ -3730,7 +3744,7 @@
         <v>446099.08462500002</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G3" s="19">
         <v>0.45</v>
@@ -3748,12 +3762,12 @@
         <v>321191.34093000001</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G4" s="19">
         <v>0.25</v>
       </c>
-      <c r="K4" s="42"/>
+      <c r="K4" s="41"/>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="9" t="s">
@@ -3767,12 +3781,12 @@
         <v>214127.56062</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G5" s="19">
         <v>0.18</v>
       </c>
-      <c r="K5" s="42"/>
+      <c r="K5" s="41"/>
       <c r="L5" s="12"/>
     </row>
     <row r="6" spans="1:12">
@@ -3787,12 +3801,12 @@
         <v>465349.48267499992</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G6" s="19">
         <v>0.12</v>
       </c>
-      <c r="K6" s="42"/>
+      <c r="K6" s="41"/>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="7" t="s">
@@ -3805,7 +3819,7 @@
         <f>$G10*$G$2*$G4</f>
         <v>258527.49037499996</v>
       </c>
-      <c r="K7" s="42"/>
+      <c r="K7" s="41"/>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="7" t="s">
@@ -3819,12 +3833,12 @@
         <v>186139.79306999996</v>
       </c>
       <c r="F8" s="22" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G8" s="23" t="s">
-        <v>43</v>
-      </c>
-      <c r="K8" s="42"/>
+        <v>45</v>
+      </c>
+      <c r="K8" s="41"/>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="9" t="s">
@@ -3838,13 +3852,13 @@
         <v>124093.19537999998</v>
       </c>
       <c r="F9" s="36" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G9" s="37">
         <v>59479877.950000003</v>
       </c>
       <c r="I9" s="24"/>
-      <c r="K9" s="42"/>
+      <c r="K9" s="41"/>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="5" t="s">
@@ -3858,13 +3872,13 @@
         <v>59666.039869499997</v>
       </c>
       <c r="F10" s="36" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G10" s="37">
         <v>34470332.049999997</v>
       </c>
       <c r="I10" s="24"/>
-      <c r="K10" s="42"/>
+      <c r="K10" s="41"/>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="7" t="s">
@@ -3878,13 +3892,13 @@
         <v>33147.799927499997</v>
       </c>
       <c r="F11" s="36" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G11" s="37">
         <v>4419706.6569999997</v>
       </c>
-      <c r="K11" s="42"/>
-      <c r="L11" s="42"/>
+      <c r="K11" s="41"/>
+      <c r="L11" s="41"/>
     </row>
     <row r="12" spans="1:12" ht="13.5" customHeight="1">
       <c r="A12" s="7" t="s">
@@ -3898,7 +3912,7 @@
         <v>23866.415947799997</v>
       </c>
       <c r="F12" s="36" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G12" s="37">
         <v>1009270</v>
@@ -3952,7 +3966,7 @@
         <v>7569.5249999999996</v>
       </c>
       <c r="F15" s="38" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G15" s="37">
         <v>16191735</v>
@@ -3970,7 +3984,7 @@
         <v>5450.0579999999991</v>
       </c>
       <c r="F16" s="36" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G16" s="37">
         <v>5209870</v>
@@ -4094,7 +4108,7 @@
       <c r="B26" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="C26" s="41">
+      <c r="C26" s="40">
         <f>$G$15*$G$2*$G3</f>
         <v>218588.42249999999</v>
       </c>
@@ -4118,7 +4132,7 @@
       <c r="B28" t="s">
         <v>13</v>
       </c>
-      <c r="C28" s="40">
+      <c r="C28" s="39">
         <f>$G$15*$G$2*$G5</f>
         <v>87435.368999999992</v>
       </c>
@@ -4202,7 +4216,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="25" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:1">

--- a/DATASOURCE.xlsx
+++ b/DATASOURCE.xlsx
@@ -1,16 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30125"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3B59E5F3-156E-4E00-881B-82CC51C71E19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mat\Desktop\TP-IO-main\TP-IO-main\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD906B51-4887-4E8C-9495-90A9AF500908}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="17640" tabRatio="500" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SETS" sheetId="1" r:id="rId1"/>
-    <sheet name="CAPACIDADES" sheetId="3" r:id="rId2"/>
-    <sheet name="PRODUCTOS" sheetId="2" r:id="rId3"/>
+    <sheet name="CAPACIDADES" sheetId="2" r:id="rId2"/>
+    <sheet name="PRODUCTOS" sheetId="3" r:id="rId3"/>
     <sheet name="DESCREMA" sheetId="4" r:id="rId4"/>
     <sheet name="COSTOS" sheetId="5" r:id="rId5"/>
     <sheet name="DEMANDA" sheetId="6" r:id="rId6"/>
@@ -32,11 +37,8 @@
     <definedName name="PLANTA">SETS!$A$2:$A$4</definedName>
     <definedName name="PRODUCTOS">SETS!$C$2:$C$9</definedName>
   </definedNames>
-  <calcPr calcId="191028" iterateDelta="1E-4"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -48,6 +50,9 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -55,8 +60,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="62">
   <si>
     <t>PLANTA</t>
   </si>
@@ -148,12 +175,6 @@
     <t>COSTO_LD_SF</t>
   </si>
   <si>
-    <t>38.61</t>
-  </si>
-  <si>
-    <t>34.75</t>
-  </si>
-  <si>
     <t>COSTO</t>
   </si>
   <si>
@@ -215,6 +236,39 @@
   </si>
   <si>
     <t>LECHE_DISPONIBLE</t>
+  </si>
+  <si>
+    <t>Compra por dia de la empresa</t>
+  </si>
+  <si>
+    <t>Multiplicador foro</t>
+  </si>
+  <si>
+    <t>Dias de octubre</t>
+  </si>
+  <si>
+    <t>Disponibilidad</t>
+  </si>
+  <si>
+    <t>Valor final</t>
+  </si>
+  <si>
+    <t>BASE</t>
+  </si>
+  <si>
+    <t>INDICE 2025</t>
+  </si>
+  <si>
+    <t>INDICE ENERO - MARZO 2026</t>
+  </si>
+  <si>
+    <t>INDICE ABRIL-OCTUBRE 2026</t>
+  </si>
+  <si>
+    <t>ACUMULADO TOTAL</t>
+  </si>
+  <si>
+    <t>ACTUALIZADO</t>
   </si>
 </sst>
 </file>
@@ -256,7 +310,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -281,14 +335,8 @@
         <bgColor rgb="FF33CCCC"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="21">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -402,6 +450,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -431,21 +494,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="thin">
         <color auto="1"/>
@@ -465,65 +513,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -531,70 +520,70 @@
   </cellStyleXfs>
   <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="3" xfId="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -686,10 +675,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -724,153 +713,55 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme>
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
                 <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
                 <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
                 <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
                 <a:lumMod val="102000"/>
                 <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
                 <a:lumMod val="100000"/>
                 <a:shade val="100000"/>
               </a:schemeClr>
@@ -878,33 +769,24 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
                 <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
@@ -917,13 +799,7 @@
           <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -933,15 +809,13 @@
         <a:solidFill>
           <a:schemeClr val="phClr">
             <a:tint val="95000"/>
-            <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
               </a:schemeClr>
@@ -949,7 +823,6 @@
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
               </a:schemeClr>
@@ -957,22 +830,17 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="63000"/>
-                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
@@ -981,93 +849,93 @@
   <dimension ref="A1:F9"/>
   <sheetFormatPr defaultColWidth="10.5703125" defaultRowHeight="15"/>
   <cols>
-    <col min="3" max="3" width="11.85546875" customWidth="1"/>
+    <col min="3" max="3" width="11.85546875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="9" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="7" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="7" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="7" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="7" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="9" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1078,103 +946,103 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I4"/>
   <sheetFormatPr defaultColWidth="10.5703125" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="25.28515625" customWidth="1"/>
-    <col min="3" max="3" width="28.7109375" customWidth="1"/>
-    <col min="4" max="4" width="18.85546875" customWidth="1"/>
-    <col min="5" max="5" width="21.5703125" customWidth="1"/>
-    <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="18.85546875" customWidth="1"/>
+    <col min="2" max="2" width="25.28515625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="28.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="18.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="21.5703125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="18.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="18.85546875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="11">
         <v>1200000</v>
       </c>
-      <c r="C2" s="10">
+      <c r="C2" s="11">
         <v>200000</v>
       </c>
-      <c r="D2" s="10">
+      <c r="D2" s="11">
         <v>150000</v>
       </c>
-      <c r="E2" s="10">
+      <c r="E2" s="11">
         <v>70000</v>
       </c>
-      <c r="F2" s="11">
+      <c r="F2" s="12">
         <v>300000</v>
       </c>
-      <c r="G2" s="12"/>
+      <c r="G2" s="13"/>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="10">
+      <c r="B3" s="11">
         <v>1100000</v>
       </c>
-      <c r="C3" s="10">
+      <c r="C3" s="11">
         <v>120000</v>
       </c>
-      <c r="D3" s="10">
+      <c r="D3" s="11">
         <v>200000</v>
       </c>
-      <c r="E3" s="10">
+      <c r="E3" s="11">
         <v>90000</v>
       </c>
-      <c r="F3" s="11">
+      <c r="F3" s="12">
         <v>250000</v>
       </c>
-      <c r="G3" s="12"/>
+      <c r="G3" s="13"/>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="10">
+      <c r="B4" s="11">
         <v>1350000</v>
       </c>
-      <c r="C4" s="10">
+      <c r="C4" s="11">
         <v>110000</v>
       </c>
-      <c r="D4" s="10">
+      <c r="D4" s="11">
         <v>0</v>
       </c>
-      <c r="E4" s="10">
+      <c r="E4" s="11">
         <v>0</v>
       </c>
-      <c r="F4" s="11">
+      <c r="F4" s="12">
         <v>250000</v>
       </c>
-      <c r="G4" s="12"/>
+      <c r="G4" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1183,111 +1051,112 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultColWidth="10.5703125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" customWidth="1"/>
-    <col min="2" max="2" width="20.42578125" customWidth="1"/>
-    <col min="3" max="3" width="15.28515625" customWidth="1"/>
+    <col min="1" max="1" width="10.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16.5703125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="27" t="s">
+      <c r="B1" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="27" t="s">
+      <c r="C1" s="14" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="34">
+      <c r="B2" s="15">
         <v>1.0629999999999999</v>
       </c>
-      <c r="C2" s="31">
+      <c r="C2" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="31" t="s">
+      <c r="A3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="34">
+      <c r="B3" s="15">
         <v>1.0629999999999999</v>
       </c>
-      <c r="C3" s="31">
+      <c r="C3" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="31" t="s">
+      <c r="A4" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="34">
+      <c r="B4" s="15">
         <v>8.7550000000000008</v>
       </c>
-      <c r="C4" s="31">
+      <c r="C4" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="31" t="s">
+      <c r="A5" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="34">
+      <c r="B5" s="15">
         <v>12.25</v>
       </c>
-      <c r="C5" s="31">
+      <c r="C5" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="31" t="s">
+      <c r="A6" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="34">
+      <c r="B6" s="15">
         <v>12.25</v>
       </c>
-      <c r="C6" s="31">
+      <c r="C6" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="31" t="s">
+      <c r="A7" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="34">
-        <v>34.0277777777778</v>
-      </c>
-      <c r="C7" s="31">
+      <c r="B7" s="15">
+        <f>12.5/0.36</f>
+        <v>34.722222222222221</v>
+      </c>
+      <c r="C7" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="34">
+      <c r="B8" s="15">
         <v>7.2450000000000001</v>
       </c>
-      <c r="C8" s="31">
+      <c r="C8" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="33" t="s">
+      <c r="A9" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="35">
+      <c r="B9" s="16">
         <v>2.395</v>
       </c>
-      <c r="C9" s="33">
+      <c r="C9" s="9">
         <v>1</v>
       </c>
     </row>
@@ -1299,42 +1168,92 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultColWidth="10.5703125" defaultRowHeight="13.9"/>
+  <dimension ref="A1:K3"/>
+  <sheetFormatPr defaultColWidth="10.5703125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.5703125" style="44"/>
-    <col min="2" max="2" width="22.7109375" style="44" customWidth="1"/>
-    <col min="3" max="3" width="13.140625" customWidth="1"/>
+    <col min="1" max="1" width="10.5703125" style="17"/>
+    <col min="2" max="2" width="22.7109375" style="17" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" style="1" customWidth="1"/>
+    <col min="4" max="9" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="43" t="s">
+      <c r="B1" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="K1" t="s">
+      <c r="D1" s="42" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1" s="42" t="s">
+        <v>57</v>
+      </c>
+      <c r="F1" s="42" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1" s="42" t="s">
+        <v>59</v>
+      </c>
+      <c r="H1" s="42" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1" s="42" t="s">
+        <v>61</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="15">
-      <c r="A2" s="43" t="s">
+    <row r="2" spans="1:11">
+      <c r="A2" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="43" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="15">
-      <c r="A3" s="43" t="s">
+      <c r="B2" s="18">
+        <v>39.619999999999997</v>
+      </c>
+      <c r="D2" s="44">
+        <v>20</v>
+      </c>
+      <c r="E2" s="44">
+        <v>37.5</v>
+      </c>
+      <c r="F2" s="44">
+        <f>(1.0208*1.0228*1.1015-1)*100</f>
+        <v>15.004777535999981</v>
+      </c>
+      <c r="G2" s="44">
+        <v>25.28</v>
+      </c>
+      <c r="H2" s="44" cm="1">
+        <f t="array" ref="H2">(PRODUCT((E2:G2/100+1))-1)*100</f>
+        <v>98.107229783513588</v>
+      </c>
+      <c r="I2" s="44">
+        <f>D2*($H$2/100+1)</f>
+        <v>39.621445956702715</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="43" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="15"/>
+      <c r="B3" s="18">
+        <v>35.659999999999997</v>
+      </c>
+      <c r="D3" s="44">
+        <v>18</v>
+      </c>
+      <c r="E3" s="44"/>
+      <c r="F3" s="44"/>
+      <c r="G3" s="44"/>
+      <c r="H3" s="44"/>
+      <c r="I3" s="44">
+        <f>D3*($H$2/100+1)</f>
+        <v>35.659301361032448</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -1344,2340 +1263,2340 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:I97"/>
-  <sheetFormatPr defaultColWidth="10.5703125" defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultColWidth="10.5703125" defaultRowHeight="15"/>
   <cols>
-    <col min="4" max="4" width="14.5703125" customWidth="1"/>
-    <col min="5" max="5" width="10.5703125" style="13"/>
-    <col min="6" max="6" width="15.28515625" customWidth="1"/>
-    <col min="7" max="7" width="13.5703125" customWidth="1"/>
-    <col min="8" max="8" width="20.85546875" customWidth="1"/>
-    <col min="9" max="9" width="18.42578125" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5703125" style="19"/>
+    <col min="6" max="6" width="15.28515625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5703125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="20.85546875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.42578125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="H1" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="G1" s="27" t="s">
+      <c r="I1" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="H1" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="I1" s="27" t="s">
-        <v>35</v>
-      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="15">
-        <f>G2*H2*I2</f>
+      <c r="D2" s="21">
+        <f t="shared" ref="D2:D33" si="0">G2*H2*I2</f>
         <v>25.3729245</v>
       </c>
-      <c r="G2" s="28">
+      <c r="G2" s="22">
         <v>24164.69</v>
       </c>
-      <c r="H2" s="30">
-        <v>1.05</v>
-      </c>
-      <c r="I2" s="31">
+      <c r="H2" s="23">
+        <v>1.05</v>
+      </c>
+      <c r="I2" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="15">
-        <f>G3*H3*I3</f>
+      <c r="D3" s="21">
+        <f t="shared" si="0"/>
         <v>82.609086000000005</v>
       </c>
-      <c r="G3" s="28">
+      <c r="G3" s="22">
         <v>78675.320000000007</v>
       </c>
-      <c r="H3" s="30">
-        <v>1.05</v>
-      </c>
-      <c r="I3" s="31">
+      <c r="H3" s="23">
+        <v>1.05</v>
+      </c>
+      <c r="I3" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="15">
-        <f>G4*H4*I4</f>
+      <c r="D4" s="21">
+        <f t="shared" si="0"/>
         <v>155.10067649999999</v>
       </c>
-      <c r="G4" s="28">
+      <c r="G4" s="22">
         <v>147714.93</v>
       </c>
-      <c r="H4" s="30">
-        <v>1.05</v>
-      </c>
-      <c r="I4" s="31">
+      <c r="H4" s="23">
+        <v>1.05</v>
+      </c>
+      <c r="I4" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="15">
-        <f>G5*H5*I5</f>
+      <c r="D5" s="21">
+        <f t="shared" si="0"/>
         <v>174.88678200000001</v>
       </c>
-      <c r="G5" s="28">
+      <c r="G5" s="22">
         <v>166558.84</v>
       </c>
-      <c r="H5" s="30">
-        <v>1.05</v>
-      </c>
-      <c r="I5" s="31">
+      <c r="H5" s="23">
+        <v>1.05</v>
+      </c>
+      <c r="I5" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="15">
-        <f>G6*H6*I6</f>
+      <c r="D6" s="21">
+        <f t="shared" si="0"/>
         <v>115.80117150000001</v>
       </c>
-      <c r="G6" s="28">
+      <c r="G6" s="22">
         <v>110286.83</v>
       </c>
-      <c r="H6" s="30">
-        <v>1.05</v>
-      </c>
-      <c r="I6" s="31">
+      <c r="H6" s="23">
+        <v>1.05</v>
+      </c>
+      <c r="I6" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="15">
-        <f>G7*H7*I7</f>
+      <c r="D7" s="21">
+        <f t="shared" si="0"/>
         <v>85.763286000000008</v>
       </c>
-      <c r="G7" s="28">
+      <c r="G7" s="22">
         <v>81679.320000000007</v>
       </c>
-      <c r="H7" s="30">
-        <v>1.05</v>
-      </c>
-      <c r="I7" s="31">
+      <c r="H7" s="23">
+        <v>1.05</v>
+      </c>
+      <c r="I7" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="15">
-        <f>G8*H8*I8</f>
+      <c r="D8" s="21">
+        <f t="shared" si="0"/>
         <v>109.718406</v>
       </c>
-      <c r="G8" s="28">
+      <c r="G8" s="22">
         <v>104493.72</v>
       </c>
-      <c r="H8" s="30">
-        <v>1.05</v>
-      </c>
-      <c r="I8" s="31">
+      <c r="H8" s="23">
+        <v>1.05</v>
+      </c>
+      <c r="I8" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="C9" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="15">
-        <f>G9*H9*I9</f>
+      <c r="D9" s="21">
+        <f t="shared" si="0"/>
         <v>107.01490800000002</v>
       </c>
-      <c r="G9" s="28">
+      <c r="G9" s="22">
         <v>101918.96</v>
       </c>
-      <c r="H9" s="30">
-        <v>1.05</v>
-      </c>
-      <c r="I9" s="31">
+      <c r="H9" s="23">
+        <v>1.05</v>
+      </c>
+      <c r="I9" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C10" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="15">
-        <f>G10*H10*I10</f>
+      <c r="D10" s="21">
+        <f t="shared" si="0"/>
         <v>97.121787000000012</v>
       </c>
-      <c r="G10" s="28">
+      <c r="G10" s="22">
         <v>92496.94</v>
       </c>
-      <c r="H10" s="30">
-        <v>1.05</v>
-      </c>
-      <c r="I10" s="31">
+      <c r="H10" s="23">
+        <v>1.05</v>
+      </c>
+      <c r="I10" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="15">
-        <f>G11*H11*I11</f>
+      <c r="D11" s="21">
+        <f t="shared" si="0"/>
         <v>48.599680500000005</v>
       </c>
-      <c r="G11" s="28">
+      <c r="G11" s="22">
         <v>46285.41</v>
       </c>
-      <c r="H11" s="30">
-        <v>1.05</v>
-      </c>
-      <c r="I11" s="31">
+      <c r="H11" s="23">
+        <v>1.05</v>
+      </c>
+      <c r="I11" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D12" s="15">
-        <f>G12*H12*I12</f>
+      <c r="D12" s="21">
+        <f t="shared" si="0"/>
         <v>136.95717000000002</v>
       </c>
-      <c r="G12" s="28">
+      <c r="G12" s="22">
         <v>130435.4</v>
       </c>
-      <c r="H12" s="30">
-        <v>1.05</v>
-      </c>
-      <c r="I12" s="31">
+      <c r="H12" s="23">
+        <v>1.05</v>
+      </c>
+      <c r="I12" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C13" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="D13" s="15">
-        <f>G13*H13*I13</f>
+      <c r="D13" s="21">
+        <f t="shared" si="0"/>
         <v>123.56915550000001</v>
       </c>
-      <c r="G13" s="28">
+      <c r="G13" s="22">
         <v>117684.91</v>
       </c>
-      <c r="H13" s="30">
-        <v>1.05</v>
-      </c>
-      <c r="I13" s="31">
+      <c r="H13" s="23">
+        <v>1.05</v>
+      </c>
+      <c r="I13" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="14" t="s">
+      <c r="B14" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="C14" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="D14" s="15">
-        <f>G14*H14*I14</f>
+      <c r="D14" s="21">
+        <f t="shared" si="0"/>
         <v>25.3729245</v>
       </c>
-      <c r="G14" s="28">
+      <c r="G14" s="22">
         <v>24164.69</v>
       </c>
-      <c r="H14" s="30">
-        <v>1.05</v>
-      </c>
-      <c r="I14" s="31">
+      <c r="H14" s="23">
+        <v>1.05</v>
+      </c>
+      <c r="I14" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D15" s="15">
-        <f>G15*H15*I15</f>
+      <c r="D15" s="21">
+        <f t="shared" si="0"/>
         <v>82.609086000000005</v>
       </c>
-      <c r="G15" s="28">
+      <c r="G15" s="22">
         <v>78675.320000000007</v>
       </c>
-      <c r="H15" s="30">
-        <v>1.05</v>
-      </c>
-      <c r="I15" s="31">
+      <c r="H15" s="23">
+        <v>1.05</v>
+      </c>
+      <c r="I15" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D16" s="15">
-        <f>G16*H16*I16</f>
+      <c r="D16" s="21">
+        <f t="shared" si="0"/>
         <v>155.10067649999999</v>
       </c>
-      <c r="G16" s="28">
+      <c r="G16" s="22">
         <v>147714.93</v>
       </c>
-      <c r="H16" s="30">
-        <v>1.05</v>
-      </c>
-      <c r="I16" s="31">
+      <c r="H16" s="23">
+        <v>1.05</v>
+      </c>
+      <c r="I16" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B17" s="16" t="s">
+      <c r="B17" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="16" t="s">
+      <c r="C17" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="D17" s="15">
-        <f>G17*H17*I17</f>
+      <c r="D17" s="21">
+        <f t="shared" si="0"/>
         <v>174.88678200000001</v>
       </c>
-      <c r="G17" s="28">
+      <c r="G17" s="22">
         <v>166558.84</v>
       </c>
-      <c r="H17" s="30">
-        <v>1.05</v>
-      </c>
-      <c r="I17" s="31">
+      <c r="H17" s="23">
+        <v>1.05</v>
+      </c>
+      <c r="I17" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B18" s="14" t="s">
+      <c r="B18" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="C18" s="14" t="s">
+      <c r="C18" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="D18" s="15">
-        <f>G18*H18*I18</f>
+      <c r="D18" s="21">
+        <f t="shared" si="0"/>
         <v>115.80117150000001</v>
       </c>
-      <c r="G18" s="28">
+      <c r="G18" s="22">
         <v>110286.83</v>
       </c>
-      <c r="H18" s="30">
-        <v>1.05</v>
-      </c>
-      <c r="I18" s="31">
+      <c r="H18" s="23">
+        <v>1.05</v>
+      </c>
+      <c r="I18" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D19" s="15">
-        <f>G19*H19*I19</f>
+      <c r="D19" s="21">
+        <f t="shared" si="0"/>
         <v>85.763286000000008</v>
       </c>
-      <c r="G19" s="28">
+      <c r="G19" s="22">
         <v>81679.320000000007</v>
       </c>
-      <c r="H19" s="30">
-        <v>1.05</v>
-      </c>
-      <c r="I19" s="31">
+      <c r="H19" s="23">
+        <v>1.05</v>
+      </c>
+      <c r="I19" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D20" s="15">
-        <f>G20*H20*I20</f>
+      <c r="D20" s="21">
+        <f t="shared" si="0"/>
         <v>109.718406</v>
       </c>
-      <c r="G20" s="28">
+      <c r="G20" s="22">
         <v>104493.72</v>
       </c>
-      <c r="H20" s="30">
-        <v>1.05</v>
-      </c>
-      <c r="I20" s="31">
+      <c r="H20" s="23">
+        <v>1.05</v>
+      </c>
+      <c r="I20" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B21" s="16" t="s">
+      <c r="B21" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="C21" s="16" t="s">
+      <c r="C21" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="D21" s="15">
-        <f>G21*H21*I21</f>
+      <c r="D21" s="21">
+        <f t="shared" si="0"/>
         <v>107.01490800000002</v>
       </c>
-      <c r="G21" s="28">
+      <c r="G21" s="22">
         <v>101918.96</v>
       </c>
-      <c r="H21" s="30">
-        <v>1.05</v>
-      </c>
-      <c r="I21" s="31">
+      <c r="H21" s="23">
+        <v>1.05</v>
+      </c>
+      <c r="I21" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="6" t="s">
+      <c r="A22" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B22" s="14" t="s">
+      <c r="B22" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="C22" s="14" t="s">
+      <c r="C22" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="D22" s="15">
-        <f>G22*H22*I22</f>
+      <c r="D22" s="21">
+        <f t="shared" si="0"/>
         <v>97.121787000000012</v>
       </c>
-      <c r="G22" s="28">
+      <c r="G22" s="22">
         <v>92496.94</v>
       </c>
-      <c r="H22" s="30">
-        <v>1.05</v>
-      </c>
-      <c r="I22" s="31">
+      <c r="H22" s="23">
+        <v>1.05</v>
+      </c>
+      <c r="I22" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="6" t="s">
+      <c r="A23" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D23" s="15">
-        <f>G23*H23*I23</f>
+      <c r="D23" s="21">
+        <f t="shared" si="0"/>
         <v>48.599680500000005</v>
       </c>
-      <c r="G23" s="28">
+      <c r="G23" s="22">
         <v>46285.41</v>
       </c>
-      <c r="H23" s="30">
-        <v>1.05</v>
-      </c>
-      <c r="I23" s="31">
+      <c r="H23" s="23">
+        <v>1.05</v>
+      </c>
+      <c r="I23" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D24" s="15">
-        <f>G24*H24*I24</f>
+      <c r="D24" s="21">
+        <f t="shared" si="0"/>
         <v>136.95717000000002</v>
       </c>
-      <c r="G24" s="28">
+      <c r="G24" s="22">
         <v>130435.4</v>
       </c>
-      <c r="H24" s="30">
-        <v>1.05</v>
-      </c>
-      <c r="I24" s="31">
+      <c r="H24" s="23">
+        <v>1.05</v>
+      </c>
+      <c r="I24" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B25" s="16" t="s">
+      <c r="B25" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="C25" s="16" t="s">
+      <c r="C25" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="D25" s="15">
-        <f>G25*H25*I25</f>
+      <c r="D25" s="21">
+        <f t="shared" si="0"/>
         <v>123.56915550000001</v>
       </c>
-      <c r="G25" s="28">
+      <c r="G25" s="22">
         <v>117684.91</v>
       </c>
-      <c r="H25" s="30">
-        <v>1.05</v>
-      </c>
-      <c r="I25" s="31">
+      <c r="H25" s="23">
+        <v>1.05</v>
+      </c>
+      <c r="I25" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="7" t="s">
+      <c r="A26" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C26" s="14" t="s">
+      <c r="C26" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="D26" s="15">
-        <f>G26*H26*I26</f>
+      <c r="D26" s="21">
+        <f t="shared" si="0"/>
         <v>24.16469</v>
       </c>
-      <c r="G26" s="28">
+      <c r="G26" s="22">
         <v>24164.69</v>
       </c>
-      <c r="H26" s="30">
+      <c r="H26" s="23">
         <v>1</v>
       </c>
-      <c r="I26" s="31">
+      <c r="I26" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="7" t="s">
+      <c r="A27" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B27" s="7" t="s">
+      <c r="B27" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D27" s="15">
-        <f>G27*H27*I27</f>
+      <c r="D27" s="21">
+        <f t="shared" si="0"/>
         <v>78.675320000000013</v>
       </c>
-      <c r="G27" s="28">
+      <c r="G27" s="22">
         <v>78675.320000000007</v>
       </c>
-      <c r="H27" s="30">
+      <c r="H27" s="23">
         <v>1</v>
       </c>
-      <c r="I27" s="31">
+      <c r="I27" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" s="7" t="s">
+      <c r="A28" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B28" s="7" t="s">
+      <c r="B28" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D28" s="15">
-        <f>G28*H28*I28</f>
+      <c r="D28" s="21">
+        <f t="shared" si="0"/>
         <v>147.71493000000001</v>
       </c>
-      <c r="G28" s="28">
+      <c r="G28" s="22">
         <v>147714.93</v>
       </c>
-      <c r="H28" s="30">
+      <c r="H28" s="23">
         <v>1</v>
       </c>
-      <c r="I28" s="31">
+      <c r="I28" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" s="7" t="s">
+      <c r="A29" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B29" s="9" t="s">
+      <c r="B29" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C29" s="16" t="s">
+      <c r="C29" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="D29" s="15">
-        <f>G29*H29*I29</f>
+      <c r="D29" s="21">
+        <f t="shared" si="0"/>
         <v>166.55884</v>
       </c>
-      <c r="G29" s="28">
+      <c r="G29" s="22">
         <v>166558.84</v>
       </c>
-      <c r="H29" s="30">
+      <c r="H29" s="23">
         <v>1</v>
       </c>
-      <c r="I29" s="31">
+      <c r="I29" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" s="7" t="s">
+      <c r="A30" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C30" s="14" t="s">
+      <c r="C30" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="D30" s="15">
-        <f>G30*H30*I30</f>
+      <c r="D30" s="21">
+        <f t="shared" si="0"/>
         <v>110.28683000000001</v>
       </c>
-      <c r="G30" s="28">
+      <c r="G30" s="22">
         <v>110286.83</v>
       </c>
-      <c r="H30" s="30">
+      <c r="H30" s="23">
         <v>1</v>
       </c>
-      <c r="I30" s="31">
+      <c r="I30" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="31" spans="1:9">
-      <c r="A31" s="7" t="s">
+      <c r="A31" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B31" s="7" t="s">
+      <c r="B31" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D31" s="15">
-        <f>G31*H31*I31</f>
+      <c r="D31" s="21">
+        <f t="shared" si="0"/>
         <v>81.679320000000004</v>
       </c>
-      <c r="G31" s="28">
+      <c r="G31" s="22">
         <v>81679.320000000007</v>
       </c>
-      <c r="H31" s="30">
+      <c r="H31" s="23">
         <v>1</v>
       </c>
-      <c r="I31" s="31">
+      <c r="I31" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" s="7" t="s">
+      <c r="A32" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B32" s="7" t="s">
+      <c r="B32" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D32" s="15">
-        <f>G32*H32*I32</f>
+      <c r="D32" s="21">
+        <f t="shared" si="0"/>
         <v>104.49372000000001</v>
       </c>
-      <c r="G32" s="28">
+      <c r="G32" s="22">
         <v>104493.72</v>
       </c>
-      <c r="H32" s="30">
+      <c r="H32" s="23">
         <v>1</v>
       </c>
-      <c r="I32" s="31">
+      <c r="I32" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="33" spans="1:9">
-      <c r="A33" s="7" t="s">
+      <c r="A33" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B33" s="9" t="s">
+      <c r="B33" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C33" s="16" t="s">
+      <c r="C33" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="D33" s="15">
-        <f>G33*H33*I33</f>
+      <c r="D33" s="21">
+        <f t="shared" si="0"/>
         <v>101.91896000000001</v>
       </c>
-      <c r="G33" s="28">
+      <c r="G33" s="22">
         <v>101918.96</v>
       </c>
-      <c r="H33" s="30">
+      <c r="H33" s="23">
         <v>1</v>
       </c>
-      <c r="I33" s="31">
+      <c r="I33" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="34" spans="1:9">
-      <c r="A34" s="7" t="s">
+      <c r="A34" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="B34" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C34" s="14" t="s">
+      <c r="C34" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="D34" s="15">
-        <f>G34*H34*I34</f>
+      <c r="D34" s="21">
+        <f t="shared" ref="D34:D65" si="1">G34*H34*I34</f>
         <v>92.496940000000009</v>
       </c>
-      <c r="G34" s="28">
+      <c r="G34" s="22">
         <v>92496.94</v>
       </c>
-      <c r="H34" s="30">
+      <c r="H34" s="23">
         <v>1</v>
       </c>
-      <c r="I34" s="31">
+      <c r="I34" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="35" spans="1:9">
-      <c r="A35" s="7" t="s">
+      <c r="A35" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B35" s="7" t="s">
+      <c r="B35" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C35" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D35" s="15">
-        <f>G35*H35*I35</f>
+      <c r="D35" s="21">
+        <f t="shared" si="1"/>
         <v>46.285410000000006</v>
       </c>
-      <c r="G35" s="28">
+      <c r="G35" s="22">
         <v>46285.41</v>
       </c>
-      <c r="H35" s="30">
+      <c r="H35" s="23">
         <v>1</v>
       </c>
-      <c r="I35" s="31">
+      <c r="I35" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="36" spans="1:9">
-      <c r="A36" s="7" t="s">
+      <c r="A36" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B36" s="7" t="s">
+      <c r="B36" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C36" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D36" s="15">
-        <f>G36*H36*I36</f>
+      <c r="D36" s="21">
+        <f t="shared" si="1"/>
         <v>130.43539999999999</v>
       </c>
-      <c r="G36" s="28">
+      <c r="G36" s="22">
         <v>130435.4</v>
       </c>
-      <c r="H36" s="30">
+      <c r="H36" s="23">
         <v>1</v>
       </c>
-      <c r="I36" s="31">
+      <c r="I36" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="37" spans="1:9">
-      <c r="A37" s="9" t="s">
+      <c r="A37" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B37" s="9" t="s">
+      <c r="B37" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C37" s="16" t="s">
+      <c r="C37" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="D37" s="15">
-        <f>G37*H37*I37</f>
+      <c r="D37" s="21">
+        <f t="shared" si="1"/>
         <v>117.68491</v>
       </c>
-      <c r="G37" s="28">
+      <c r="G37" s="22">
         <v>117684.91</v>
       </c>
-      <c r="H37" s="30">
+      <c r="H37" s="23">
         <v>1</v>
       </c>
-      <c r="I37" s="31">
+      <c r="I37" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="38" spans="1:9">
-      <c r="A38" s="5" t="s">
+      <c r="A38" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="B38" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C38" s="14" t="s">
+      <c r="C38" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="D38" s="15">
-        <f>G38*H38*I38</f>
+      <c r="D38" s="21">
+        <f t="shared" si="1"/>
         <v>24.16469</v>
       </c>
-      <c r="G38" s="28">
+      <c r="G38" s="22">
         <v>24164.69</v>
       </c>
-      <c r="H38" s="30">
+      <c r="H38" s="23">
         <v>1</v>
       </c>
-      <c r="I38" s="31">
+      <c r="I38" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="39" spans="1:9">
-      <c r="A39" s="7" t="s">
+      <c r="A39" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B39" s="7" t="s">
+      <c r="B39" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C39" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D39" s="15">
-        <f>G39*H39*I39</f>
+      <c r="D39" s="21">
+        <f t="shared" si="1"/>
         <v>78.675320000000013</v>
       </c>
-      <c r="G39" s="28">
+      <c r="G39" s="22">
         <v>78675.320000000007</v>
       </c>
-      <c r="H39" s="30">
+      <c r="H39" s="23">
         <v>1</v>
       </c>
-      <c r="I39" s="31">
+      <c r="I39" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="40" spans="1:9">
-      <c r="A40" s="7" t="s">
+      <c r="A40" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B40" s="7" t="s">
+      <c r="B40" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C40" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D40" s="15">
-        <f>G40*H40*I40</f>
+      <c r="D40" s="21">
+        <f t="shared" si="1"/>
         <v>147.71493000000001</v>
       </c>
-      <c r="G40" s="28">
+      <c r="G40" s="22">
         <v>147714.93</v>
       </c>
-      <c r="H40" s="30">
+      <c r="H40" s="23">
         <v>1</v>
       </c>
-      <c r="I40" s="31">
+      <c r="I40" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="41" spans="1:9">
-      <c r="A41" s="7" t="s">
+      <c r="A41" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B41" s="9" t="s">
+      <c r="B41" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C41" s="16" t="s">
+      <c r="C41" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="D41" s="15">
-        <f>G41*H41*I41</f>
+      <c r="D41" s="21">
+        <f t="shared" si="1"/>
         <v>166.55884</v>
       </c>
-      <c r="G41" s="28">
+      <c r="G41" s="22">
         <v>166558.84</v>
       </c>
-      <c r="H41" s="30">
+      <c r="H41" s="23">
         <v>1</v>
       </c>
-      <c r="I41" s="31">
+      <c r="I41" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="42" spans="1:9">
-      <c r="A42" s="7" t="s">
+      <c r="A42" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B42" s="5" t="s">
+      <c r="B42" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C42" s="14" t="s">
+      <c r="C42" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="D42" s="15">
-        <f>G42*H42*I42</f>
+      <c r="D42" s="21">
+        <f t="shared" si="1"/>
         <v>110.28683000000001</v>
       </c>
-      <c r="G42" s="28">
+      <c r="G42" s="22">
         <v>110286.83</v>
       </c>
-      <c r="H42" s="30">
+      <c r="H42" s="23">
         <v>1</v>
       </c>
-      <c r="I42" s="31">
+      <c r="I42" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="43" spans="1:9">
-      <c r="A43" s="7" t="s">
+      <c r="A43" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B43" s="7" t="s">
+      <c r="B43" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C43" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D43" s="15">
-        <f>G43*H43*I43</f>
+      <c r="D43" s="21">
+        <f t="shared" si="1"/>
         <v>81.679320000000004</v>
       </c>
-      <c r="G43" s="28">
+      <c r="G43" s="22">
         <v>81679.320000000007</v>
       </c>
-      <c r="H43" s="30">
+      <c r="H43" s="23">
         <v>1</v>
       </c>
-      <c r="I43" s="31">
+      <c r="I43" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="44" spans="1:9">
-      <c r="A44" s="7" t="s">
+      <c r="A44" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B44" s="7" t="s">
+      <c r="B44" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C44" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D44" s="15">
-        <f>G44*H44*I44</f>
+      <c r="D44" s="21">
+        <f t="shared" si="1"/>
         <v>104.49372000000001</v>
       </c>
-      <c r="G44" s="28">
+      <c r="G44" s="22">
         <v>104493.72</v>
       </c>
-      <c r="H44" s="30">
+      <c r="H44" s="23">
         <v>1</v>
       </c>
-      <c r="I44" s="31">
+      <c r="I44" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="45" spans="1:9">
-      <c r="A45" s="7" t="s">
+      <c r="A45" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B45" s="9" t="s">
+      <c r="B45" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C45" s="16" t="s">
+      <c r="C45" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="D45" s="15">
-        <f>G45*H45*I45</f>
+      <c r="D45" s="21">
+        <f t="shared" si="1"/>
         <v>101.91896000000001</v>
       </c>
-      <c r="G45" s="28">
+      <c r="G45" s="22">
         <v>101918.96</v>
       </c>
-      <c r="H45" s="30">
+      <c r="H45" s="23">
         <v>1</v>
       </c>
-      <c r="I45" s="31">
+      <c r="I45" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="46" spans="1:9">
-      <c r="A46" s="7" t="s">
+      <c r="A46" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B46" s="5" t="s">
+      <c r="B46" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C46" s="14" t="s">
+      <c r="C46" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="D46" s="15">
-        <f>G46*H46*I46</f>
+      <c r="D46" s="21">
+        <f t="shared" si="1"/>
         <v>92.496940000000009</v>
       </c>
-      <c r="G46" s="28">
+      <c r="G46" s="22">
         <v>92496.94</v>
       </c>
-      <c r="H46" s="30">
+      <c r="H46" s="23">
         <v>1</v>
       </c>
-      <c r="I46" s="31">
+      <c r="I46" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="47" spans="1:9">
-      <c r="A47" s="7" t="s">
+      <c r="A47" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B47" s="7" t="s">
+      <c r="B47" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C47" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D47" s="15">
-        <f>G47*H47*I47</f>
+      <c r="D47" s="21">
+        <f t="shared" si="1"/>
         <v>46.285410000000006</v>
       </c>
-      <c r="G47" s="28">
+      <c r="G47" s="22">
         <v>46285.41</v>
       </c>
-      <c r="H47" s="30">
+      <c r="H47" s="23">
         <v>1</v>
       </c>
-      <c r="I47" s="31">
+      <c r="I47" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="48" spans="1:9">
-      <c r="A48" s="7" t="s">
+      <c r="A48" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B48" s="7" t="s">
+      <c r="B48" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C48" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D48" s="15">
-        <f>G48*H48*I48</f>
+      <c r="D48" s="21">
+        <f t="shared" si="1"/>
         <v>130.43539999999999</v>
       </c>
-      <c r="G48" s="28">
+      <c r="G48" s="22">
         <v>130435.4</v>
       </c>
-      <c r="H48" s="30">
+      <c r="H48" s="23">
         <v>1</v>
       </c>
-      <c r="I48" s="31">
+      <c r="I48" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="49" spans="1:9">
-      <c r="A49" s="9" t="s">
+      <c r="A49" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B49" s="9" t="s">
+      <c r="B49" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C49" s="16" t="s">
+      <c r="C49" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="D49" s="15">
-        <f>G49*H49*I49</f>
+      <c r="D49" s="21">
+        <f t="shared" si="1"/>
         <v>117.68491</v>
       </c>
-      <c r="G49" s="28">
+      <c r="G49" s="22">
         <v>117684.91</v>
       </c>
-      <c r="H49" s="30">
+      <c r="H49" s="23">
         <v>1</v>
       </c>
-      <c r="I49" s="31">
+      <c r="I49" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="50" spans="1:9">
-      <c r="A50" s="5" t="s">
+      <c r="A50" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B50" s="5" t="s">
+      <c r="B50" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C50" s="14" t="s">
+      <c r="C50" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="D50" s="15">
-        <f>G50*H50*I50</f>
+      <c r="D50" s="21">
+        <f t="shared" si="1"/>
         <v>25.3729245</v>
       </c>
-      <c r="G50" s="28">
+      <c r="G50" s="22">
         <v>24164.69</v>
       </c>
-      <c r="H50" s="30">
-        <v>1.05</v>
-      </c>
-      <c r="I50" s="31">
+      <c r="H50" s="23">
+        <v>1.05</v>
+      </c>
+      <c r="I50" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="51" spans="1:9">
-      <c r="A51" s="7" t="s">
+      <c r="A51" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B51" s="7" t="s">
+      <c r="B51" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C51" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D51" s="15">
-        <f>G51*H51*I51</f>
+      <c r="D51" s="21">
+        <f t="shared" si="1"/>
         <v>82.609086000000005</v>
       </c>
-      <c r="G51" s="28">
+      <c r="G51" s="22">
         <v>78675.320000000007</v>
       </c>
-      <c r="H51" s="30">
-        <v>1.05</v>
-      </c>
-      <c r="I51" s="31">
+      <c r="H51" s="23">
+        <v>1.05</v>
+      </c>
+      <c r="I51" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="52" spans="1:9">
-      <c r="A52" s="7" t="s">
+      <c r="A52" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B52" s="7" t="s">
+      <c r="B52" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C52" t="s">
+      <c r="C52" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D52" s="15">
-        <f>G52*H52*I52</f>
+      <c r="D52" s="21">
+        <f t="shared" si="1"/>
         <v>155.10067649999999</v>
       </c>
-      <c r="G52" s="28">
+      <c r="G52" s="22">
         <v>147714.93</v>
       </c>
-      <c r="H52" s="30">
-        <v>1.05</v>
-      </c>
-      <c r="I52" s="31">
+      <c r="H52" s="23">
+        <v>1.05</v>
+      </c>
+      <c r="I52" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="53" spans="1:9">
-      <c r="A53" s="7" t="s">
+      <c r="A53" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B53" s="9" t="s">
+      <c r="B53" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C53" s="16" t="s">
+      <c r="C53" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="D53" s="15">
-        <f>G53*H53*I53</f>
+      <c r="D53" s="21">
+        <f t="shared" si="1"/>
         <v>174.88678200000001</v>
       </c>
-      <c r="G53" s="28">
+      <c r="G53" s="22">
         <v>166558.84</v>
       </c>
-      <c r="H53" s="30">
-        <v>1.05</v>
-      </c>
-      <c r="I53" s="31">
+      <c r="H53" s="23">
+        <v>1.05</v>
+      </c>
+      <c r="I53" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="54" spans="1:9">
-      <c r="A54" s="7" t="s">
+      <c r="A54" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B54" s="5" t="s">
+      <c r="B54" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C54" s="14" t="s">
+      <c r="C54" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="D54" s="15">
-        <f>G54*H54*I54</f>
+      <c r="D54" s="21">
+        <f t="shared" si="1"/>
         <v>115.80117150000001</v>
       </c>
-      <c r="G54" s="28">
+      <c r="G54" s="22">
         <v>110286.83</v>
       </c>
-      <c r="H54" s="30">
-        <v>1.05</v>
-      </c>
-      <c r="I54" s="31">
+      <c r="H54" s="23">
+        <v>1.05</v>
+      </c>
+      <c r="I54" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="55" spans="1:9">
-      <c r="A55" s="7" t="s">
+      <c r="A55" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B55" s="7" t="s">
+      <c r="B55" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C55" t="s">
+      <c r="C55" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D55" s="15">
-        <f>G55*H55*I55</f>
+      <c r="D55" s="21">
+        <f t="shared" si="1"/>
         <v>85.763286000000008</v>
       </c>
-      <c r="G55" s="28">
+      <c r="G55" s="22">
         <v>81679.320000000007</v>
       </c>
-      <c r="H55" s="30">
-        <v>1.05</v>
-      </c>
-      <c r="I55" s="31">
+      <c r="H55" s="23">
+        <v>1.05</v>
+      </c>
+      <c r="I55" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="56" spans="1:9">
-      <c r="A56" s="7" t="s">
+      <c r="A56" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B56" s="7" t="s">
+      <c r="B56" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C56" t="s">
+      <c r="C56" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D56" s="15">
-        <f>G56*H56*I56</f>
+      <c r="D56" s="21">
+        <f t="shared" si="1"/>
         <v>109.718406</v>
       </c>
-      <c r="G56" s="28">
+      <c r="G56" s="22">
         <v>104493.72</v>
       </c>
-      <c r="H56" s="30">
-        <v>1.05</v>
-      </c>
-      <c r="I56" s="31">
+      <c r="H56" s="23">
+        <v>1.05</v>
+      </c>
+      <c r="I56" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="57" spans="1:9">
-      <c r="A57" s="7" t="s">
+      <c r="A57" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B57" s="9" t="s">
+      <c r="B57" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C57" s="16" t="s">
+      <c r="C57" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="D57" s="15">
-        <f>G57*H57*I57</f>
+      <c r="D57" s="21">
+        <f t="shared" si="1"/>
         <v>107.01490800000002</v>
       </c>
-      <c r="G57" s="28">
+      <c r="G57" s="22">
         <v>101918.96</v>
       </c>
-      <c r="H57" s="30">
-        <v>1.05</v>
-      </c>
-      <c r="I57" s="31">
+      <c r="H57" s="23">
+        <v>1.05</v>
+      </c>
+      <c r="I57" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="58" spans="1:9">
-      <c r="A58" s="7" t="s">
+      <c r="A58" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B58" s="5" t="s">
+      <c r="B58" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C58" s="14" t="s">
+      <c r="C58" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="D58" s="15">
-        <f>G58*H58*I58</f>
+      <c r="D58" s="21">
+        <f t="shared" si="1"/>
         <v>97.121787000000012</v>
       </c>
-      <c r="G58" s="28">
+      <c r="G58" s="22">
         <v>92496.94</v>
       </c>
-      <c r="H58" s="30">
-        <v>1.05</v>
-      </c>
-      <c r="I58" s="31">
+      <c r="H58" s="23">
+        <v>1.05</v>
+      </c>
+      <c r="I58" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="59" spans="1:9">
-      <c r="A59" s="7" t="s">
+      <c r="A59" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B59" s="7" t="s">
+      <c r="B59" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C59" t="s">
+      <c r="C59" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D59" s="15">
-        <f>G59*H59*I59</f>
+      <c r="D59" s="21">
+        <f t="shared" si="1"/>
         <v>48.599680500000005</v>
       </c>
-      <c r="G59" s="28">
+      <c r="G59" s="22">
         <v>46285.41</v>
       </c>
-      <c r="H59" s="30">
-        <v>1.05</v>
-      </c>
-      <c r="I59" s="31">
+      <c r="H59" s="23">
+        <v>1.05</v>
+      </c>
+      <c r="I59" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="60" spans="1:9">
-      <c r="A60" s="7" t="s">
+      <c r="A60" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B60" s="7" t="s">
+      <c r="B60" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C60" t="s">
+      <c r="C60" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D60" s="15">
-        <f>G60*H60*I60</f>
+      <c r="D60" s="21">
+        <f t="shared" si="1"/>
         <v>136.95717000000002</v>
       </c>
-      <c r="G60" s="28">
+      <c r="G60" s="22">
         <v>130435.4</v>
       </c>
-      <c r="H60" s="30">
-        <v>1.05</v>
-      </c>
-      <c r="I60" s="31">
+      <c r="H60" s="23">
+        <v>1.05</v>
+      </c>
+      <c r="I60" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="61" spans="1:9">
-      <c r="A61" s="9" t="s">
+      <c r="A61" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B61" s="9" t="s">
+      <c r="B61" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C61" s="16" t="s">
+      <c r="C61" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="D61" s="15">
-        <f>G61*H61*I61</f>
+      <c r="D61" s="21">
+        <f t="shared" si="1"/>
         <v>123.56915550000001</v>
       </c>
-      <c r="G61" s="28">
+      <c r="G61" s="22">
         <v>117684.91</v>
       </c>
-      <c r="H61" s="30">
-        <v>1.05</v>
-      </c>
-      <c r="I61" s="31">
+      <c r="H61" s="23">
+        <v>1.05</v>
+      </c>
+      <c r="I61" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="62" spans="1:9">
-      <c r="A62" s="5" t="s">
+      <c r="A62" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B62" s="5" t="s">
+      <c r="B62" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C62" s="14" t="s">
+      <c r="C62" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="D62" s="15">
-        <f>G62*H62*I62</f>
+      <c r="D62" s="21">
+        <f t="shared" si="1"/>
         <v>25.3729245</v>
       </c>
-      <c r="G62" s="28">
+      <c r="G62" s="22">
         <v>24164.69</v>
       </c>
-      <c r="H62" s="30">
-        <v>1.05</v>
-      </c>
-      <c r="I62" s="31">
+      <c r="H62" s="23">
+        <v>1.05</v>
+      </c>
+      <c r="I62" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="63" spans="1:9">
-      <c r="A63" s="7" t="s">
+      <c r="A63" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B63" s="7" t="s">
+      <c r="B63" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C63" t="s">
+      <c r="C63" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D63" s="15">
-        <f>G63*H63*I63</f>
+      <c r="D63" s="21">
+        <f t="shared" si="1"/>
         <v>82.609086000000005</v>
       </c>
-      <c r="G63" s="28">
+      <c r="G63" s="22">
         <v>78675.320000000007</v>
       </c>
-      <c r="H63" s="30">
-        <v>1.05</v>
-      </c>
-      <c r="I63" s="31">
+      <c r="H63" s="23">
+        <v>1.05</v>
+      </c>
+      <c r="I63" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="64" spans="1:9">
-      <c r="A64" s="7" t="s">
+      <c r="A64" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B64" s="7" t="s">
+      <c r="B64" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C64" t="s">
+      <c r="C64" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D64" s="15">
-        <f>G64*H64*I64</f>
+      <c r="D64" s="21">
+        <f t="shared" si="1"/>
         <v>155.10067649999999</v>
       </c>
-      <c r="G64" s="28">
+      <c r="G64" s="22">
         <v>147714.93</v>
       </c>
-      <c r="H64" s="30">
-        <v>1.05</v>
-      </c>
-      <c r="I64" s="31">
+      <c r="H64" s="23">
+        <v>1.05</v>
+      </c>
+      <c r="I64" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="65" spans="1:9">
-      <c r="A65" s="7" t="s">
+      <c r="A65" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B65" s="9" t="s">
+      <c r="B65" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C65" s="16" t="s">
+      <c r="C65" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="D65" s="15">
-        <f>G65*H65*I65</f>
+      <c r="D65" s="21">
+        <f t="shared" si="1"/>
         <v>174.88678200000001</v>
       </c>
-      <c r="G65" s="28">
+      <c r="G65" s="22">
         <v>166558.84</v>
       </c>
-      <c r="H65" s="30">
-        <v>1.05</v>
-      </c>
-      <c r="I65" s="31">
+      <c r="H65" s="23">
+        <v>1.05</v>
+      </c>
+      <c r="I65" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="66" spans="1:9">
-      <c r="A66" s="7" t="s">
+      <c r="A66" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B66" s="5" t="s">
+      <c r="B66" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C66" s="14" t="s">
+      <c r="C66" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="D66" s="15">
-        <f>G66*H66*I66</f>
+      <c r="D66" s="21">
+        <f t="shared" ref="D66:D97" si="2">G66*H66*I66</f>
         <v>115.80117150000001</v>
       </c>
-      <c r="G66" s="28">
+      <c r="G66" s="22">
         <v>110286.83</v>
       </c>
-      <c r="H66" s="30">
-        <v>1.05</v>
-      </c>
-      <c r="I66" s="31">
+      <c r="H66" s="23">
+        <v>1.05</v>
+      </c>
+      <c r="I66" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="67" spans="1:9">
-      <c r="A67" s="7" t="s">
+      <c r="A67" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B67" s="7" t="s">
+      <c r="B67" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C67" t="s">
+      <c r="C67" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D67" s="15">
-        <f>G67*H67*I67</f>
+      <c r="D67" s="21">
+        <f t="shared" si="2"/>
         <v>85.763286000000008</v>
       </c>
-      <c r="G67" s="28">
+      <c r="G67" s="22">
         <v>81679.320000000007</v>
       </c>
-      <c r="H67" s="30">
-        <v>1.05</v>
-      </c>
-      <c r="I67" s="31">
+      <c r="H67" s="23">
+        <v>1.05</v>
+      </c>
+      <c r="I67" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="68" spans="1:9">
-      <c r="A68" s="7" t="s">
+      <c r="A68" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B68" s="7" t="s">
+      <c r="B68" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C68" t="s">
+      <c r="C68" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D68" s="15">
-        <f>G68*H68*I68</f>
+      <c r="D68" s="21">
+        <f t="shared" si="2"/>
         <v>109.718406</v>
       </c>
-      <c r="G68" s="28">
+      <c r="G68" s="22">
         <v>104493.72</v>
       </c>
-      <c r="H68" s="30">
-        <v>1.05</v>
-      </c>
-      <c r="I68" s="31">
+      <c r="H68" s="23">
+        <v>1.05</v>
+      </c>
+      <c r="I68" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="69" spans="1:9">
-      <c r="A69" s="7" t="s">
+      <c r="A69" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B69" s="9" t="s">
+      <c r="B69" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C69" s="16" t="s">
+      <c r="C69" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="D69" s="15">
-        <f>G69*H69*I69</f>
+      <c r="D69" s="21">
+        <f t="shared" si="2"/>
         <v>107.01490800000002</v>
       </c>
-      <c r="G69" s="28">
+      <c r="G69" s="22">
         <v>101918.96</v>
       </c>
-      <c r="H69" s="30">
-        <v>1.05</v>
-      </c>
-      <c r="I69" s="31">
+      <c r="H69" s="23">
+        <v>1.05</v>
+      </c>
+      <c r="I69" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="70" spans="1:9">
-      <c r="A70" s="7" t="s">
+      <c r="A70" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B70" s="5" t="s">
+      <c r="B70" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C70" s="14" t="s">
+      <c r="C70" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="D70" s="15">
-        <f>G70*H70*I70</f>
+      <c r="D70" s="21">
+        <f t="shared" si="2"/>
         <v>97.121787000000012</v>
       </c>
-      <c r="G70" s="28">
+      <c r="G70" s="22">
         <v>92496.94</v>
       </c>
-      <c r="H70" s="30">
-        <v>1.05</v>
-      </c>
-      <c r="I70" s="31">
+      <c r="H70" s="23">
+        <v>1.05</v>
+      </c>
+      <c r="I70" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="71" spans="1:9">
-      <c r="A71" s="7" t="s">
+      <c r="A71" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B71" s="7" t="s">
+      <c r="B71" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C71" t="s">
+      <c r="C71" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D71" s="15">
-        <f>G71*H71*I71</f>
+      <c r="D71" s="21">
+        <f t="shared" si="2"/>
         <v>48.599680500000005</v>
       </c>
-      <c r="G71" s="28">
+      <c r="G71" s="22">
         <v>46285.41</v>
       </c>
-      <c r="H71" s="30">
-        <v>1.05</v>
-      </c>
-      <c r="I71" s="31">
+      <c r="H71" s="23">
+        <v>1.05</v>
+      </c>
+      <c r="I71" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="72" spans="1:9">
-      <c r="A72" s="7" t="s">
+      <c r="A72" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B72" s="7" t="s">
+      <c r="B72" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C72" t="s">
+      <c r="C72" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D72" s="15">
-        <f>G72*H72*I72</f>
+      <c r="D72" s="21">
+        <f t="shared" si="2"/>
         <v>136.95717000000002</v>
       </c>
-      <c r="G72" s="28">
+      <c r="G72" s="22">
         <v>130435.4</v>
       </c>
-      <c r="H72" s="30">
-        <v>1.05</v>
-      </c>
-      <c r="I72" s="31">
+      <c r="H72" s="23">
+        <v>1.05</v>
+      </c>
+      <c r="I72" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="73" spans="1:9">
-      <c r="A73" s="9" t="s">
+      <c r="A73" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B73" s="9" t="s">
+      <c r="B73" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C73" s="16" t="s">
+      <c r="C73" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="D73" s="15">
-        <f>G73*H73*I73</f>
+      <c r="D73" s="21">
+        <f t="shared" si="2"/>
         <v>123.56915550000001</v>
       </c>
-      <c r="G73" s="28">
+      <c r="G73" s="22">
         <v>117684.91</v>
       </c>
-      <c r="H73" s="30">
-        <v>1.05</v>
-      </c>
-      <c r="I73" s="31">
+      <c r="H73" s="23">
+        <v>1.05</v>
+      </c>
+      <c r="I73" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="74" spans="1:9">
-      <c r="A74" s="5" t="s">
+      <c r="A74" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B74" s="5" t="s">
+      <c r="B74" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C74" s="14" t="s">
+      <c r="C74" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="D74" s="15">
-        <f>G74*H74*I74</f>
+      <c r="D74" s="21">
+        <f t="shared" si="2"/>
         <v>25.3729245</v>
       </c>
-      <c r="G74" s="28">
+      <c r="G74" s="22">
         <v>24164.69</v>
       </c>
-      <c r="H74" s="30">
-        <v>1.05</v>
-      </c>
-      <c r="I74" s="31">
+      <c r="H74" s="23">
+        <v>1.05</v>
+      </c>
+      <c r="I74" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="75" spans="1:9">
-      <c r="A75" s="7" t="s">
+      <c r="A75" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B75" s="7" t="s">
+      <c r="B75" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C75" t="s">
+      <c r="C75" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D75" s="15">
-        <f>G75*H75*I75</f>
+      <c r="D75" s="21">
+        <f t="shared" si="2"/>
         <v>82.609086000000005</v>
       </c>
-      <c r="G75" s="28">
+      <c r="G75" s="22">
         <v>78675.320000000007</v>
       </c>
-      <c r="H75" s="30">
-        <v>1.05</v>
-      </c>
-      <c r="I75" s="31">
+      <c r="H75" s="23">
+        <v>1.05</v>
+      </c>
+      <c r="I75" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="76" spans="1:9">
-      <c r="A76" s="7" t="s">
+      <c r="A76" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B76" s="7" t="s">
+      <c r="B76" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C76" t="s">
+      <c r="C76" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D76" s="15">
-        <f>G76*H76*I76</f>
+      <c r="D76" s="21">
+        <f t="shared" si="2"/>
         <v>155.10067649999999</v>
       </c>
-      <c r="G76" s="28">
+      <c r="G76" s="22">
         <v>147714.93</v>
       </c>
-      <c r="H76" s="30">
-        <v>1.05</v>
-      </c>
-      <c r="I76" s="31">
+      <c r="H76" s="23">
+        <v>1.05</v>
+      </c>
+      <c r="I76" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="77" spans="1:9">
-      <c r="A77" s="7" t="s">
+      <c r="A77" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B77" s="9" t="s">
+      <c r="B77" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C77" s="16" t="s">
+      <c r="C77" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="D77" s="15">
-        <f>G77*H77*I77</f>
+      <c r="D77" s="21">
+        <f t="shared" si="2"/>
         <v>174.88678200000001</v>
       </c>
-      <c r="G77" s="28">
+      <c r="G77" s="22">
         <v>166558.84</v>
       </c>
-      <c r="H77" s="30">
-        <v>1.05</v>
-      </c>
-      <c r="I77" s="31">
+      <c r="H77" s="23">
+        <v>1.05</v>
+      </c>
+      <c r="I77" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="78" spans="1:9">
-      <c r="A78" s="7" t="s">
+      <c r="A78" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B78" s="5" t="s">
+      <c r="B78" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C78" s="14" t="s">
+      <c r="C78" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="D78" s="15">
-        <f>G78*H78*I78</f>
+      <c r="D78" s="21">
+        <f t="shared" si="2"/>
         <v>115.80117150000001</v>
       </c>
-      <c r="G78" s="28">
+      <c r="G78" s="22">
         <v>110286.83</v>
       </c>
-      <c r="H78" s="30">
-        <v>1.05</v>
-      </c>
-      <c r="I78" s="31">
+      <c r="H78" s="23">
+        <v>1.05</v>
+      </c>
+      <c r="I78" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="79" spans="1:9">
-      <c r="A79" s="7" t="s">
+      <c r="A79" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B79" s="7" t="s">
+      <c r="B79" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C79" t="s">
+      <c r="C79" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D79" s="15">
-        <f>G79*H79*I79</f>
+      <c r="D79" s="21">
+        <f t="shared" si="2"/>
         <v>85.763286000000008</v>
       </c>
-      <c r="G79" s="28">
+      <c r="G79" s="22">
         <v>81679.320000000007</v>
       </c>
-      <c r="H79" s="30">
-        <v>1.05</v>
-      </c>
-      <c r="I79" s="31">
+      <c r="H79" s="23">
+        <v>1.05</v>
+      </c>
+      <c r="I79" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="80" spans="1:9">
-      <c r="A80" s="7" t="s">
+      <c r="A80" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B80" s="7" t="s">
+      <c r="B80" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C80" t="s">
+      <c r="C80" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D80" s="15">
-        <f>G80*H80*I80</f>
+      <c r="D80" s="21">
+        <f t="shared" si="2"/>
         <v>109.718406</v>
       </c>
-      <c r="G80" s="28">
+      <c r="G80" s="22">
         <v>104493.72</v>
       </c>
-      <c r="H80" s="30">
-        <v>1.05</v>
-      </c>
-      <c r="I80" s="31">
+      <c r="H80" s="23">
+        <v>1.05</v>
+      </c>
+      <c r="I80" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="81" spans="1:9">
-      <c r="A81" s="7" t="s">
+      <c r="A81" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B81" s="9" t="s">
+      <c r="B81" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C81" s="16" t="s">
+      <c r="C81" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="D81" s="15">
-        <f>G81*H81*I81</f>
+      <c r="D81" s="21">
+        <f t="shared" si="2"/>
         <v>107.01490800000002</v>
       </c>
-      <c r="G81" s="28">
+      <c r="G81" s="22">
         <v>101918.96</v>
       </c>
-      <c r="H81" s="30">
-        <v>1.05</v>
-      </c>
-      <c r="I81" s="31">
+      <c r="H81" s="23">
+        <v>1.05</v>
+      </c>
+      <c r="I81" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="82" spans="1:9">
-      <c r="A82" s="7" t="s">
+      <c r="A82" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B82" s="5" t="s">
+      <c r="B82" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C82" s="14" t="s">
+      <c r="C82" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="D82" s="15">
-        <f>G82*H82*I82</f>
+      <c r="D82" s="21">
+        <f t="shared" si="2"/>
         <v>97.121787000000012</v>
       </c>
-      <c r="G82" s="28">
+      <c r="G82" s="22">
         <v>92496.94</v>
       </c>
-      <c r="H82" s="30">
-        <v>1.05</v>
-      </c>
-      <c r="I82" s="31">
+      <c r="H82" s="23">
+        <v>1.05</v>
+      </c>
+      <c r="I82" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="83" spans="1:9">
-      <c r="A83" s="7" t="s">
+      <c r="A83" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B83" s="7" t="s">
+      <c r="B83" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C83" t="s">
+      <c r="C83" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D83" s="15">
-        <f>G83*H83*I83</f>
+      <c r="D83" s="21">
+        <f t="shared" si="2"/>
         <v>48.599680500000005</v>
       </c>
-      <c r="G83" s="28">
+      <c r="G83" s="22">
         <v>46285.41</v>
       </c>
-      <c r="H83" s="30">
-        <v>1.05</v>
-      </c>
-      <c r="I83" s="31">
+      <c r="H83" s="23">
+        <v>1.05</v>
+      </c>
+      <c r="I83" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="84" spans="1:9">
-      <c r="A84" s="7" t="s">
+      <c r="A84" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B84" s="7" t="s">
+      <c r="B84" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C84" t="s">
+      <c r="C84" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D84" s="15">
-        <f>G84*H84*I84</f>
+      <c r="D84" s="21">
+        <f t="shared" si="2"/>
         <v>136.95717000000002</v>
       </c>
-      <c r="G84" s="28">
+      <c r="G84" s="22">
         <v>130435.4</v>
       </c>
-      <c r="H84" s="30">
-        <v>1.05</v>
-      </c>
-      <c r="I84" s="31">
+      <c r="H84" s="23">
+        <v>1.05</v>
+      </c>
+      <c r="I84" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="85" spans="1:9">
-      <c r="A85" s="9" t="s">
+      <c r="A85" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="B85" s="9" t="s">
+      <c r="B85" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C85" s="16" t="s">
+      <c r="C85" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="D85" s="15">
-        <f>G85*H85*I85</f>
+      <c r="D85" s="21">
+        <f t="shared" si="2"/>
         <v>123.56915550000001</v>
       </c>
-      <c r="G85" s="28">
+      <c r="G85" s="22">
         <v>117684.91</v>
       </c>
-      <c r="H85" s="30">
-        <v>1.05</v>
-      </c>
-      <c r="I85" s="31">
+      <c r="H85" s="23">
+        <v>1.05</v>
+      </c>
+      <c r="I85" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="86" spans="1:9">
-      <c r="A86" s="5" t="s">
+      <c r="A86" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B86" s="5" t="s">
+      <c r="B86" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C86" s="14" t="s">
+      <c r="C86" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="D86" s="15">
-        <f>G86*H86*I86</f>
+      <c r="D86" s="21">
+        <f t="shared" si="2"/>
         <v>25.3729245</v>
       </c>
-      <c r="G86" s="28">
+      <c r="G86" s="22">
         <v>24164.69</v>
       </c>
-      <c r="H86" s="30">
-        <v>1.05</v>
-      </c>
-      <c r="I86" s="31">
+      <c r="H86" s="23">
+        <v>1.05</v>
+      </c>
+      <c r="I86" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="87" spans="1:9">
-      <c r="A87" s="7" t="s">
+      <c r="A87" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B87" s="7" t="s">
+      <c r="B87" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C87" t="s">
+      <c r="C87" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D87" s="15">
-        <f>G87*H87*I87</f>
+      <c r="D87" s="21">
+        <f t="shared" si="2"/>
         <v>82.609086000000005</v>
       </c>
-      <c r="G87" s="28">
+      <c r="G87" s="22">
         <v>78675.320000000007</v>
       </c>
-      <c r="H87" s="30">
-        <v>1.05</v>
-      </c>
-      <c r="I87" s="31">
+      <c r="H87" s="23">
+        <v>1.05</v>
+      </c>
+      <c r="I87" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="88" spans="1:9">
-      <c r="A88" s="7" t="s">
+      <c r="A88" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B88" s="7" t="s">
+      <c r="B88" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C88" t="s">
+      <c r="C88" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D88" s="15">
-        <f>G88*H88*I88</f>
+      <c r="D88" s="21">
+        <f t="shared" si="2"/>
         <v>155.10067649999999</v>
       </c>
-      <c r="G88" s="28">
+      <c r="G88" s="22">
         <v>147714.93</v>
       </c>
-      <c r="H88" s="30">
-        <v>1.05</v>
-      </c>
-      <c r="I88" s="31">
+      <c r="H88" s="23">
+        <v>1.05</v>
+      </c>
+      <c r="I88" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="89" spans="1:9">
-      <c r="A89" s="7" t="s">
+      <c r="A89" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B89" s="9" t="s">
+      <c r="B89" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C89" s="16" t="s">
+      <c r="C89" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="D89" s="15">
-        <f>G89*H89*I89</f>
+      <c r="D89" s="21">
+        <f t="shared" si="2"/>
         <v>174.88678200000001</v>
       </c>
-      <c r="G89" s="28">
+      <c r="G89" s="22">
         <v>166558.84</v>
       </c>
-      <c r="H89" s="30">
-        <v>1.05</v>
-      </c>
-      <c r="I89" s="31">
+      <c r="H89" s="23">
+        <v>1.05</v>
+      </c>
+      <c r="I89" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="90" spans="1:9">
-      <c r="A90" s="7" t="s">
+      <c r="A90" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B90" s="5" t="s">
+      <c r="B90" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C90" s="14" t="s">
+      <c r="C90" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="D90" s="15">
-        <f>G90*H90*I90</f>
+      <c r="D90" s="21">
+        <f t="shared" si="2"/>
         <v>115.80117150000001</v>
       </c>
-      <c r="G90" s="28">
+      <c r="G90" s="22">
         <v>110286.83</v>
       </c>
-      <c r="H90" s="30">
-        <v>1.05</v>
-      </c>
-      <c r="I90" s="31">
+      <c r="H90" s="23">
+        <v>1.05</v>
+      </c>
+      <c r="I90" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="91" spans="1:9">
-      <c r="A91" s="7" t="s">
+      <c r="A91" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B91" s="7" t="s">
+      <c r="B91" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C91" t="s">
+      <c r="C91" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D91" s="15">
-        <f>G91*H91*I91</f>
+      <c r="D91" s="21">
+        <f t="shared" si="2"/>
         <v>85.763286000000008</v>
       </c>
-      <c r="G91" s="28">
+      <c r="G91" s="22">
         <v>81679.320000000007</v>
       </c>
-      <c r="H91" s="30">
-        <v>1.05</v>
-      </c>
-      <c r="I91" s="31">
+      <c r="H91" s="23">
+        <v>1.05</v>
+      </c>
+      <c r="I91" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="92" spans="1:9">
-      <c r="A92" s="7" t="s">
+      <c r="A92" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B92" s="7" t="s">
+      <c r="B92" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C92" t="s">
+      <c r="C92" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D92" s="15">
-        <f>G92*H92*I92</f>
+      <c r="D92" s="21">
+        <f t="shared" si="2"/>
         <v>109.718406</v>
       </c>
-      <c r="G92" s="28">
+      <c r="G92" s="22">
         <v>104493.72</v>
       </c>
-      <c r="H92" s="30">
-        <v>1.05</v>
-      </c>
-      <c r="I92" s="31">
+      <c r="H92" s="23">
+        <v>1.05</v>
+      </c>
+      <c r="I92" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="93" spans="1:9">
-      <c r="A93" s="7" t="s">
+      <c r="A93" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B93" s="9" t="s">
+      <c r="B93" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C93" s="16" t="s">
+      <c r="C93" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="D93" s="15">
-        <f>G93*H93*I93</f>
+      <c r="D93" s="21">
+        <f t="shared" si="2"/>
         <v>107.01490800000002</v>
       </c>
-      <c r="G93" s="28">
+      <c r="G93" s="22">
         <v>101918.96</v>
       </c>
-      <c r="H93" s="30">
-        <v>1.05</v>
-      </c>
-      <c r="I93" s="31">
+      <c r="H93" s="23">
+        <v>1.05</v>
+      </c>
+      <c r="I93" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="94" spans="1:9">
-      <c r="A94" s="7" t="s">
+      <c r="A94" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B94" s="5" t="s">
+      <c r="B94" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C94" s="14" t="s">
+      <c r="C94" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="D94" s="15">
-        <f>G94*H94*I94</f>
+      <c r="D94" s="21">
+        <f t="shared" si="2"/>
         <v>97.121787000000012</v>
       </c>
-      <c r="G94" s="28">
+      <c r="G94" s="22">
         <v>92496.94</v>
       </c>
-      <c r="H94" s="30">
-        <v>1.05</v>
-      </c>
-      <c r="I94" s="31">
+      <c r="H94" s="23">
+        <v>1.05</v>
+      </c>
+      <c r="I94" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="95" spans="1:9">
-      <c r="A95" s="7" t="s">
+      <c r="A95" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B95" s="7" t="s">
+      <c r="B95" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C95" t="s">
+      <c r="C95" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D95" s="15">
-        <f>G95*H95*I95</f>
+      <c r="D95" s="21">
+        <f t="shared" si="2"/>
         <v>48.599680500000005</v>
       </c>
-      <c r="G95" s="28">
+      <c r="G95" s="22">
         <v>46285.41</v>
       </c>
-      <c r="H95" s="30">
-        <v>1.05</v>
-      </c>
-      <c r="I95" s="31">
+      <c r="H95" s="23">
+        <v>1.05</v>
+      </c>
+      <c r="I95" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="96" spans="1:9">
-      <c r="A96" s="7" t="s">
+      <c r="A96" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B96" s="7" t="s">
+      <c r="B96" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C96" t="s">
+      <c r="C96" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D96" s="15">
-        <f>G96*H96*I96</f>
+      <c r="D96" s="21">
+        <f t="shared" si="2"/>
         <v>136.95717000000002</v>
       </c>
-      <c r="G96" s="28">
+      <c r="G96" s="22">
         <v>130435.4</v>
       </c>
-      <c r="H96" s="30">
-        <v>1.05</v>
-      </c>
-      <c r="I96" s="31">
+      <c r="H96" s="23">
+        <v>1.05</v>
+      </c>
+      <c r="I96" s="7">
         <v>1E-3</v>
       </c>
     </row>
     <row r="97" spans="1:9">
-      <c r="A97" s="9" t="s">
+      <c r="A97" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="B97" s="9" t="s">
+      <c r="B97" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C97" s="16" t="s">
+      <c r="C97" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="D97" s="15">
-        <f>G97*H97*I97</f>
+      <c r="D97" s="21">
+        <f t="shared" si="2"/>
         <v>123.56915550000001</v>
       </c>
-      <c r="G97" s="29">
+      <c r="G97" s="25">
         <v>117684.91</v>
       </c>
-      <c r="H97" s="32">
-        <v>1.05</v>
-      </c>
-      <c r="I97" s="33">
+      <c r="H97" s="26">
+        <v>1.05</v>
+      </c>
+      <c r="I97" s="9">
         <v>1E-3</v>
       </c>
     </row>
@@ -3692,507 +3611,507 @@
   <dimension ref="A1:L33"/>
   <sheetFormatPr defaultColWidth="10.5703125" defaultRowHeight="15"/>
   <cols>
-    <col min="3" max="3" width="15.85546875" customWidth="1"/>
-    <col min="6" max="6" width="30.28515625" customWidth="1"/>
-    <col min="7" max="7" width="21.7109375" customWidth="1"/>
-    <col min="11" max="11" width="31" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="30.28515625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="21.7109375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="31" style="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F1" s="42" t="s">
-        <v>38</v>
-      </c>
-      <c r="G1" s="42"/>
+      <c r="G1" s="40"/>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="17">
+      <c r="C2" s="27">
         <f>$G$9*$G$2*$G3</f>
         <v>802978.3523250001</v>
       </c>
-      <c r="F2" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="G2" s="19">
+      <c r="F2" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="G2" s="29">
         <v>0.03</v>
       </c>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="20">
+      <c r="C3" s="30">
         <f>$G$9*$G$2*$G4</f>
         <v>446099.08462500002</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G3" s="19">
+      <c r="F3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G3" s="29">
         <v>0.45</v>
       </c>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="20">
+      <c r="C4" s="30">
         <f>$G$9*$G$2*$G5</f>
         <v>321191.34093000001</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G4" s="19">
+      <c r="F4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G4" s="29">
         <v>0.25</v>
       </c>
-      <c r="K4" s="41"/>
+      <c r="K4" s="31"/>
     </row>
     <row r="5" spans="1:12">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="21">
+      <c r="C5" s="32">
         <f>$G$9*$G$2*$G6</f>
         <v>214127.56062</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G5" s="19">
+      <c r="F5" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G5" s="29">
         <v>0.18</v>
       </c>
-      <c r="K5" s="41"/>
-      <c r="L5" s="12"/>
+      <c r="K5" s="31"/>
+      <c r="L5" s="13"/>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="17">
+      <c r="C6" s="27">
         <f>$G$10*$G$2*$G3</f>
         <v>465349.48267499992</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G6" s="19">
+      <c r="F6" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G6" s="29">
         <v>0.12</v>
       </c>
-      <c r="K6" s="41"/>
+      <c r="K6" s="31"/>
     </row>
     <row r="7" spans="1:12">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="20">
+      <c r="C7" s="30">
         <f>$G10*$G$2*$G4</f>
         <v>258527.49037499996</v>
       </c>
-      <c r="K7" s="41"/>
+      <c r="K7" s="31"/>
     </row>
     <row r="8" spans="1:12">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="20">
+      <c r="C8" s="30">
         <f>$G$10*$G$2*$G5</f>
         <v>186139.79306999996</v>
       </c>
-      <c r="F8" s="22" t="s">
-        <v>44</v>
-      </c>
-      <c r="G8" s="23" t="s">
-        <v>45</v>
-      </c>
-      <c r="K8" s="41"/>
+      <c r="F8" s="33" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8" s="34" t="s">
+        <v>43</v>
+      </c>
+      <c r="K8" s="31"/>
     </row>
     <row r="9" spans="1:12">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="21">
+      <c r="C9" s="32">
         <f>$G$10*$G$2*$G6</f>
         <v>124093.19537999998</v>
       </c>
-      <c r="F9" s="36" t="s">
-        <v>46</v>
-      </c>
-      <c r="G9" s="37">
+      <c r="F9" s="35" t="s">
+        <v>44</v>
+      </c>
+      <c r="G9" s="36">
         <v>59479877.950000003</v>
       </c>
-      <c r="I9" s="24"/>
-      <c r="K9" s="41"/>
+      <c r="I9" s="37"/>
+      <c r="K9" s="31"/>
     </row>
     <row r="10" spans="1:12">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="B10" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="17">
+      <c r="C10" s="27">
         <f>$G$11*$G$2*$G3</f>
         <v>59666.039869499997</v>
       </c>
-      <c r="F10" s="36" t="s">
-        <v>47</v>
-      </c>
-      <c r="G10" s="37">
+      <c r="F10" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="G10" s="36">
         <v>34470332.049999997</v>
       </c>
-      <c r="I10" s="24"/>
-      <c r="K10" s="41"/>
+      <c r="I10" s="37"/>
+      <c r="K10" s="31"/>
     </row>
     <row r="11" spans="1:12">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="20">
+      <c r="C11" s="30">
         <f>$G$11*$G$2*$G4</f>
         <v>33147.799927499997</v>
       </c>
-      <c r="F11" s="36" t="s">
-        <v>48</v>
-      </c>
-      <c r="G11" s="37">
+      <c r="F11" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="G11" s="36">
         <v>4419706.6569999997</v>
       </c>
-      <c r="K11" s="41"/>
-      <c r="L11" s="41"/>
+      <c r="K11" s="31"/>
+      <c r="L11" s="31"/>
     </row>
     <row r="12" spans="1:12" ht="13.5" customHeight="1">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="20">
+      <c r="C12" s="30">
         <f>$G$11*$G$2*$G5</f>
         <v>23866.415947799997</v>
       </c>
-      <c r="F12" s="36" t="s">
-        <v>49</v>
-      </c>
-      <c r="G12" s="37">
+      <c r="F12" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="G12" s="36">
         <v>1009270</v>
       </c>
     </row>
     <row r="13" spans="1:12">
-      <c r="A13" s="9" t="s">
+      <c r="A13" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="16" t="s">
+      <c r="B13" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="21">
+      <c r="C13" s="32">
         <f>$G$11*$G$2*$G6</f>
         <v>15910.943965199998</v>
       </c>
-      <c r="F13" s="36" t="s">
+      <c r="F13" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="G13" s="37">
+      <c r="G13" s="36">
         <v>7168200</v>
       </c>
     </row>
     <row r="14" spans="1:12">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="14" t="s">
+      <c r="B14" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C14" s="17">
+      <c r="C14" s="27">
         <f>$G$12*$G$2*$G3</f>
         <v>13625.145</v>
       </c>
-      <c r="F14" s="36" t="s">
+      <c r="F14" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="G14" s="37">
+      <c r="G14" s="36">
         <v>2125000</v>
       </c>
     </row>
     <row r="15" spans="1:12">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="20">
+      <c r="C15" s="30">
         <f>$G$12*$G$2*$G4</f>
         <v>7569.5249999999996</v>
       </c>
       <c r="F15" s="38" t="s">
-        <v>50</v>
-      </c>
-      <c r="G15" s="37">
+        <v>48</v>
+      </c>
+      <c r="G15" s="36">
         <v>16191735</v>
       </c>
     </row>
     <row r="16" spans="1:12">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C16" s="20">
+      <c r="C16" s="30">
         <f>$G$12*$G$2*$G5</f>
         <v>5450.0579999999991</v>
       </c>
-      <c r="F16" s="36" t="s">
-        <v>51</v>
-      </c>
-      <c r="G16" s="37">
+      <c r="F16" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="G16" s="36">
         <v>5209870</v>
       </c>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" s="9" t="s">
+      <c r="A17" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="16" t="s">
+      <c r="B17" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="21">
+      <c r="C17" s="32">
         <f>$G$12*$G$2*$G6</f>
         <v>3633.3719999999998</v>
       </c>
     </row>
     <row r="18" spans="1:6">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="14" t="s">
+      <c r="B18" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="17">
+      <c r="C18" s="27">
         <f>$G$13*$G$2*$G3</f>
         <v>96770.7</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F18" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="7" t="s">
+      <c r="A19" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C19" s="20">
+      <c r="C19" s="30">
         <f>$G$13*$G$2*$G4</f>
         <v>53761.5</v>
       </c>
     </row>
     <row r="20" spans="1:6">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C20" s="20">
+      <c r="C20" s="30">
         <f>$G$13*$G$2*$G5</f>
         <v>38708.28</v>
       </c>
     </row>
     <row r="21" spans="1:6">
-      <c r="A21" s="9" t="s">
+      <c r="A21" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B21" s="16" t="s">
+      <c r="B21" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="C21" s="21">
+      <c r="C21" s="32">
         <f>$G$13*$G$2*$G6</f>
         <v>25805.52</v>
       </c>
     </row>
     <row r="22" spans="1:6">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B22" s="14" t="s">
+      <c r="B22" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C22" s="17">
+      <c r="C22" s="27">
         <f>$G$14*$G$2*$G3</f>
         <v>28687.5</v>
       </c>
     </row>
     <row r="23" spans="1:6">
-      <c r="A23" s="7" t="s">
+      <c r="A23" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="20">
+      <c r="C23" s="30">
         <f>$G$14*$G$2*$G4</f>
         <v>15937.5</v>
       </c>
     </row>
     <row r="24" spans="1:6">
-      <c r="A24" s="7" t="s">
+      <c r="A24" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C24" s="20">
+      <c r="C24" s="30">
         <f>$G$14*$G$2*$G5</f>
         <v>11475</v>
       </c>
     </row>
     <row r="25" spans="1:6">
-      <c r="A25" s="9" t="s">
+      <c r="A25" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B25" s="16" t="s">
+      <c r="B25" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="C25" s="20">
+      <c r="C25" s="30">
         <f>$G$14*$G$2*$G6</f>
         <v>7650</v>
       </c>
     </row>
     <row r="26" spans="1:6">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B26" s="14" t="s">
+      <c r="B26" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C26" s="40">
+      <c r="C26" s="27">
         <f>$G$15*$G$2*$G3</f>
         <v>218588.42249999999</v>
       </c>
     </row>
     <row r="27" spans="1:6">
-      <c r="A27" s="7" t="s">
+      <c r="A27" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C27" s="20">
+      <c r="C27" s="30">
         <f>$G$15*$G$2*$G4</f>
         <v>121438.0125</v>
       </c>
     </row>
     <row r="28" spans="1:6">
-      <c r="A28" s="7" t="s">
+      <c r="A28" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C28" s="39">
+      <c r="C28" s="30">
         <f>$G$15*$G$2*$G5</f>
         <v>87435.368999999992</v>
       </c>
     </row>
     <row r="29" spans="1:6">
-      <c r="A29" s="9" t="s">
+      <c r="A29" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="B29" s="16" t="s">
+      <c r="B29" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="C29" s="20">
+      <c r="C29" s="30">
         <f>$G$15*$G$2*$G6</f>
         <v>58290.245999999999</v>
       </c>
     </row>
     <row r="30" spans="1:6">
-      <c r="A30" s="5" t="s">
+      <c r="A30" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B30" s="14" t="s">
+      <c r="B30" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C30" s="17">
+      <c r="C30" s="27">
         <f>$G$16*$G$2*$G3</f>
         <v>70333.24500000001</v>
       </c>
     </row>
     <row r="31" spans="1:6">
-      <c r="A31" s="7" t="s">
+      <c r="A31" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C31" s="20">
+      <c r="C31" s="30">
         <f>$G$16*$G$2*$G4</f>
         <v>39074.025000000001</v>
       </c>
     </row>
     <row r="32" spans="1:6">
-      <c r="A32" s="7" t="s">
+      <c r="A32" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C32" s="20">
+      <c r="C32" s="30">
         <f>$G$16*$G$2*$G5</f>
         <v>28133.297999999999</v>
       </c>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" s="9" t="s">
+      <c r="A33" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="B33" s="16" t="s">
+      <c r="B33" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="C33" s="21">
+      <c r="C33" s="32">
         <f>$G$16*$G$2*$G6</f>
         <v>18755.531999999999</v>
       </c>
@@ -4208,20 +4127,55 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultColWidth="10.5703125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="17.85546875" customWidth="1"/>
+    <col min="1" max="1" width="17.85546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="16.7109375" customWidth="1"/>
+    <col min="5" max="5" width="15" customWidth="1"/>
+    <col min="6" max="7" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="25" t="s">
+    <row r="1" spans="1:7">
+      <c r="A1" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1" s="41" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1" s="41" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="2" spans="1:1">
-      <c r="A2" s="26">
-        <v>1168344890</v>
+      <c r="E1" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1" s="42" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1" s="41" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="39">
+        <f>G2</f>
+        <v>33008800</v>
+      </c>
+      <c r="C2" s="39">
+        <v>880000</v>
+      </c>
+      <c r="D2" s="39">
+        <v>1.21</v>
+      </c>
+      <c r="E2" s="39">
+        <v>31</v>
+      </c>
+      <c r="F2" s="43">
+        <v>1</v>
+      </c>
+      <c r="G2" s="39">
+        <f>C2*(D2)*E2*F2</f>
+        <v>33008800</v>
       </c>
     </row>
   </sheetData>
